--- a/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-count-two.xlsx
+++ b/OfficeIMO.TestAssets/Documents/ExcelPivotCorpus/AllErrorRanking/bottom-count-two.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\przemyslaw.klys.EVOTEC\.codex\worktrees\excel-csv-quality\OfficeIMO\OfficeIMO.TestAssets\Documents\ExcelPivotCorpus\AllErrorRanking\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2D907AC-0FAB-4014-9FAA-0526682E889B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E46A971D-333A-4A3A-B193-7A2BE6EFB9EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{728F18DF-D3D1-4185-82FB-4E6744572BBC}"/>
+    <workbookView xWindow="-98" yWindow="16170" windowWidth="28996" windowHeight="15675" xr2:uid="{43D26FE0-27CA-4D98-9C46-548E4598CEF4}"/>
   </bookViews>
   <sheets>
     <sheet name="Grouped" sheetId="2" r:id="rId1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.576851504629" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{A57E0392-F110-47B6-A5B4-CB4771907BD2}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="OfficeIMO Word COM Fixture" refreshedDate="46293.579414814812" createdVersion="6" refreshedVersion="8" minRefreshableVersion="3" recordCount="3" xr:uid="{E2D7CCDB-EC0F-456A-A119-DE6CEC4E243B}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:B4" sheet="Source"/>
   </cacheSource>
@@ -164,7 +164,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AD4B8522-8493-4450-9B70-487B148ED27F}" name="AllErrorPivot" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C3A31878-7393-4555-B809-5E5ACCFBF102}" name="AllErrorPivot" cacheId="31" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="6" indent="0" compact="0" compactData="0" multipleFieldFilters="0">
   <location ref="A4:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="2">
     <pivotField axis="axisRow" compact="0" outline="0" showAll="0" measureFilter="1">
@@ -534,7 +534,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03C10074-B7F4-4CD8-B242-5DDDB3A87C8E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A98C715-C369-48BC-BFC7-0C74C50903EA}">
   <dimension ref="A4:B7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -580,7 +580,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B164787-53E7-44A0-B25F-1B9E3B5FF154}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40223BF6-F3D2-48C8-91C5-DA6DA5AB6D92}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
